--- a/02_加值成品/九上/九上2-1_三種難度測驗卷.xlsx
+++ b/02_加值成品/九上/九上2-1_三種難度測驗卷.xlsx
@@ -490,19 +490,23 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D12"/>
+  <dimension ref="A1:H12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
-    <col width="62" customWidth="1" min="2" max="2"/>
+    <col width="54" customWidth="1" min="2" max="2"/>
     <col width="20" customWidth="1" min="3" max="3"/>
-    <col width="42" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="8" customWidth="1" min="7" max="7"/>
+    <col width="40" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>國三上學期 九上2-1 牛頓第一運動定律　測驗　★☆☆ 基礎（記憶・理解）</t>
+          <t>國三上學期 九上2-1 牛頓第一運動定律　測驗　★☆☆ 基礎（記憶・理解）（四選一單選）</t>
         </is>
       </c>
     </row>
@@ -519,16 +523,36 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
+          <t>(A)</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>(B)</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>(C)</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>(D)</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
           <t>答案</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="H2" s="2" t="inlineStr">
         <is>
           <t>解析</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="34" customHeight="1">
+    <row r="3" ht="40" customHeight="1">
       <c r="A3" s="3" t="n">
         <v>1</v>
       </c>
@@ -537,18 +561,38 @@
           <t>物體維持原運動狀態的性質是？</t>
         </is>
       </c>
-      <c r="C3" s="5" t="inlineStr">
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>等速前進</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
         <is>
           <t>慣性</t>
         </is>
       </c>
-      <c r="D3" s="4" t="inlineStr">
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>第一</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>前衝</t>
+        </is>
+      </c>
+      <c r="G3" s="5" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H3" s="4" t="inlineStr">
         <is>
           <t>固有</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="34" customHeight="1">
+    <row r="4" ht="40" customHeight="1">
       <c r="A4" s="6" t="n">
         <v>2</v>
       </c>
@@ -557,18 +601,38 @@
           <t>合力為零時靜止物體會？</t>
         </is>
       </c>
-      <c r="C4" s="8" t="inlineStr">
+      <c r="C4" s="7" t="inlineStr">
         <is>
           <t>保持靜止</t>
         </is>
       </c>
       <c r="D4" s="7" t="inlineStr">
         <is>
+          <t>質量</t>
+        </is>
+      </c>
+      <c r="E4" s="7" t="inlineStr">
+        <is>
+          <t>等速直線運動</t>
+        </is>
+      </c>
+      <c r="F4" s="7" t="inlineStr">
+        <is>
+          <t>第一</t>
+        </is>
+      </c>
+      <c r="G4" s="8" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H4" s="7" t="inlineStr">
+        <is>
           <t>靜者恆靜</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="34" customHeight="1">
+    <row r="5" ht="40" customHeight="1">
       <c r="A5" s="3" t="n">
         <v>3</v>
       </c>
@@ -577,18 +641,38 @@
           <t>合力為零時運動物體會？</t>
         </is>
       </c>
-      <c r="C5" s="5" t="inlineStr">
+      <c r="C5" s="4" t="inlineStr">
         <is>
           <t>等速直線運動</t>
         </is>
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
+          <t>慣性維持前進</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>越大</t>
+        </is>
+      </c>
+      <c r="F5" s="4" t="inlineStr">
+        <is>
+          <t>大</t>
+        </is>
+      </c>
+      <c r="G5" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H5" s="4" t="inlineStr">
+        <is>
           <t>動者恆動</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="34" customHeight="1">
+    <row r="6" ht="40" customHeight="1">
       <c r="A6" s="6" t="n">
         <v>4</v>
       </c>
@@ -597,18 +681,38 @@
           <t>牛頓第幾定律是慣性定律？</t>
         </is>
       </c>
-      <c r="C6" s="8" t="inlineStr">
+      <c r="C6" s="7" t="inlineStr">
+        <is>
+          <t>持續等速前進</t>
+        </is>
+      </c>
+      <c r="D6" s="7" t="inlineStr">
+        <is>
+          <t>等速直線運動</t>
+        </is>
+      </c>
+      <c r="E6" s="7" t="inlineStr">
+        <is>
+          <t>不是</t>
+        </is>
+      </c>
+      <c r="F6" s="7" t="inlineStr">
         <is>
           <t>第一</t>
         </is>
       </c>
-      <c r="D6" s="7" t="inlineStr">
+      <c r="G6" s="8" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H6" s="7" t="inlineStr">
         <is>
           <t>慣性</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="34" customHeight="1">
+    <row r="7" ht="40" customHeight="1">
       <c r="A7" s="3" t="n">
         <v>5</v>
       </c>
@@ -617,18 +721,38 @@
           <t>慣性大小由什麼決定？</t>
         </is>
       </c>
-      <c r="C7" s="5" t="inlineStr">
+      <c r="C7" s="4" t="inlineStr">
         <is>
           <t>質量</t>
         </is>
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
+          <t>不是</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>等速直線運動</t>
+        </is>
+      </c>
+      <c r="F7" s="4" t="inlineStr">
+        <is>
+          <t>保持靜止</t>
+        </is>
+      </c>
+      <c r="G7" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H7" s="4" t="inlineStr">
+        <is>
           <t>量度</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="34" customHeight="1">
+    <row r="8" ht="40" customHeight="1">
       <c r="A8" s="6" t="n">
         <v>6</v>
       </c>
@@ -637,18 +761,38 @@
           <t>質量越大慣性？</t>
         </is>
       </c>
-      <c r="C8" s="8" t="inlineStr">
+      <c r="C8" s="7" t="inlineStr">
+        <is>
+          <t>持續等速前進</t>
+        </is>
+      </c>
+      <c r="D8" s="7" t="inlineStr">
+        <is>
+          <t>質量大慣性大</t>
+        </is>
+      </c>
+      <c r="E8" s="7" t="inlineStr">
         <is>
           <t>越大</t>
         </is>
       </c>
-      <c r="D8" s="7" t="inlineStr">
+      <c r="F8" s="7" t="inlineStr">
+        <is>
+          <t>等速直線運動</t>
+        </is>
+      </c>
+      <c r="G8" s="8" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H8" s="7" t="inlineStr">
         <is>
           <t>越難改變</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="34" customHeight="1">
+    <row r="9" ht="40" customHeight="1">
       <c r="A9" s="3" t="n">
         <v>7</v>
       </c>
@@ -657,18 +801,38 @@
           <t>等速直線運動需要力維持嗎？</t>
         </is>
       </c>
-      <c r="C9" s="5" t="inlineStr">
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>等速直線運動</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="inlineStr">
+        <is>
+          <t>保持靜止</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr">
+        <is>
+          <t>零</t>
+        </is>
+      </c>
+      <c r="F9" s="4" t="inlineStr">
         <is>
           <t>不需要</t>
         </is>
       </c>
-      <c r="D9" s="4" t="inlineStr">
+      <c r="G9" s="5" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H9" s="4" t="inlineStr">
         <is>
           <t>慣性</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="34" customHeight="1">
+    <row r="10" ht="40" customHeight="1">
       <c r="A10" s="6" t="n">
         <v>8</v>
       </c>
@@ -677,18 +841,38 @@
           <t>安全帶利用防止慣性使人？</t>
         </is>
       </c>
-      <c r="C10" s="8" t="inlineStr">
+      <c r="C10" s="7" t="inlineStr">
         <is>
           <t>前衝</t>
         </is>
       </c>
       <c r="D10" s="7" t="inlineStr">
         <is>
+          <t>質量大慣性大</t>
+        </is>
+      </c>
+      <c r="E10" s="7" t="inlineStr">
+        <is>
+          <t>質量</t>
+        </is>
+      </c>
+      <c r="F10" s="7" t="inlineStr">
+        <is>
+          <t>等速前進</t>
+        </is>
+      </c>
+      <c r="G10" s="8" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H10" s="7" t="inlineStr">
+        <is>
           <t>保護</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="34" customHeight="1">
+    <row r="11" ht="40" customHeight="1">
       <c r="A11" s="3" t="n">
         <v>9</v>
       </c>
@@ -697,18 +881,38 @@
           <t>慣性定律是牛頓第幾定律？</t>
         </is>
       </c>
-      <c r="C11" s="5" t="inlineStr">
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>慣性</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="inlineStr">
         <is>
           <t>第一</t>
         </is>
       </c>
-      <c r="D11" s="4" t="inlineStr">
+      <c r="E11" s="4" t="inlineStr">
+        <is>
+          <t>質量</t>
+        </is>
+      </c>
+      <c r="F11" s="4" t="inlineStr">
+        <is>
+          <t>等速直線運動</t>
+        </is>
+      </c>
+      <c r="G11" s="5" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H11" s="4" t="inlineStr">
         <is>
           <t>慣性</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="34" customHeight="1">
+    <row r="12" ht="40" customHeight="1">
       <c r="A12" s="6" t="n">
         <v>10</v>
       </c>
@@ -717,12 +921,32 @@
           <t>物體不受外力時運動狀態會？</t>
         </is>
       </c>
-      <c r="C12" s="8" t="inlineStr">
+      <c r="C12" s="7" t="inlineStr">
+        <is>
+          <t>等速直線運動</t>
+        </is>
+      </c>
+      <c r="D12" s="7" t="inlineStr">
+        <is>
+          <t>慣性</t>
+        </is>
+      </c>
+      <c r="E12" s="7" t="inlineStr">
         <is>
           <t>維持不變</t>
         </is>
       </c>
-      <c r="D12" s="7" t="inlineStr">
+      <c r="F12" s="7" t="inlineStr">
+        <is>
+          <t>零</t>
+        </is>
+      </c>
+      <c r="G12" s="8" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H12" s="7" t="inlineStr">
         <is>
           <t>慣性</t>
         </is>
@@ -730,7 +954,7 @@
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A1:H1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -742,19 +966,23 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D12"/>
+  <dimension ref="A1:H12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
-    <col width="62" customWidth="1" min="2" max="2"/>
+    <col width="54" customWidth="1" min="2" max="2"/>
     <col width="20" customWidth="1" min="3" max="3"/>
-    <col width="42" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="8" customWidth="1" min="7" max="7"/>
+    <col width="40" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>國三上學期 九上2-1 牛頓第一運動定律　測驗　★★☆ 進階（應用・分析）</t>
+          <t>國三上學期 九上2-1 牛頓第一運動定律　測驗　★★☆ 進階（應用・分析）（四選一單選）</t>
         </is>
       </c>
     </row>
@@ -771,16 +999,36 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
+          <t>(A)</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>(B)</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>(C)</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>(D)</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
           <t>答案</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="H2" s="2" t="inlineStr">
         <is>
           <t>解析</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="34" customHeight="1">
+    <row r="3" ht="40" customHeight="1">
       <c r="A3" s="3" t="n">
         <v>1</v>
       </c>
@@ -789,18 +1037,38 @@
           <t>煞車時乘客前傾是因為？</t>
         </is>
       </c>
-      <c r="C3" s="5" t="inlineStr">
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>等速前進</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>慣性</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
         <is>
           <t>慣性維持前進</t>
         </is>
       </c>
-      <c r="D3" s="4" t="inlineStr">
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>第一</t>
+        </is>
+      </c>
+      <c r="G3" s="5" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H3" s="4" t="inlineStr">
         <is>
           <t>慣性</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="34" customHeight="1">
+    <row r="4" ht="40" customHeight="1">
       <c r="A4" s="6" t="n">
         <v>2</v>
       </c>
@@ -809,7 +1077,7 @@
           <t>公車起步乘客後仰因為？</t>
         </is>
       </c>
-      <c r="C4" s="8" t="inlineStr">
+      <c r="C4" s="7" t="inlineStr">
         <is>
           <t>慣性維持靜止</t>
         </is>
@@ -819,8 +1087,28 @@
           <t>慣性</t>
         </is>
       </c>
-    </row>
-    <row r="5" ht="34" customHeight="1">
+      <c r="E4" s="7" t="inlineStr">
+        <is>
+          <t>質量</t>
+        </is>
+      </c>
+      <c r="F4" s="7" t="inlineStr">
+        <is>
+          <t>第一</t>
+        </is>
+      </c>
+      <c r="G4" s="8" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H4" s="7" t="inlineStr">
+        <is>
+          <t>慣性</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="40" customHeight="1">
       <c r="A5" s="3" t="n">
         <v>3</v>
       </c>
@@ -829,18 +1117,38 @@
           <t>慣性是力嗎？</t>
         </is>
       </c>
-      <c r="C5" s="5" t="inlineStr">
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>不需要</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>質量</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>慣性維持靜止</t>
+        </is>
+      </c>
+      <c r="F5" s="4" t="inlineStr">
         <is>
           <t>不是</t>
         </is>
       </c>
-      <c r="D5" s="4" t="inlineStr">
+      <c r="G5" s="5" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H5" s="4" t="inlineStr">
         <is>
           <t>性質</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="34" customHeight="1">
+    <row r="6" ht="40" customHeight="1">
       <c r="A6" s="6" t="n">
         <v>4</v>
       </c>
@@ -849,18 +1157,38 @@
           <t>大貨車比機車難煞停因為？</t>
         </is>
       </c>
-      <c r="C6" s="8" t="inlineStr">
+      <c r="C6" s="7" t="inlineStr">
         <is>
           <t>質量大慣性大</t>
         </is>
       </c>
       <c r="D6" s="7" t="inlineStr">
         <is>
+          <t>不需要</t>
+        </is>
+      </c>
+      <c r="E6" s="7" t="inlineStr">
+        <is>
+          <t>保持靜止</t>
+        </is>
+      </c>
+      <c r="F6" s="7" t="inlineStr">
+        <is>
+          <t>維持不變</t>
+        </is>
+      </c>
+      <c r="G6" s="8" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H6" s="7" t="inlineStr">
+        <is>
           <t>質量</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="34" customHeight="1">
+    <row r="7" ht="40" customHeight="1">
       <c r="A7" s="3" t="n">
         <v>5</v>
       </c>
@@ -869,18 +1197,38 @@
           <t>太空中推一下物體會？</t>
         </is>
       </c>
-      <c r="C7" s="5" t="inlineStr">
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>等速直線運動</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>慣性</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>維持不變</t>
+        </is>
+      </c>
+      <c r="F7" s="4" t="inlineStr">
         <is>
           <t>等速前進</t>
         </is>
       </c>
-      <c r="D7" s="4" t="inlineStr">
+      <c r="G7" s="5" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H7" s="4" t="inlineStr">
         <is>
           <t>無阻力</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="34" customHeight="1">
+    <row r="8" ht="40" customHeight="1">
       <c r="A8" s="6" t="n">
         <v>6</v>
       </c>
@@ -889,18 +1237,38 @@
           <t>甩體溫計使水銀下降靠？</t>
         </is>
       </c>
-      <c r="C8" s="8" t="inlineStr">
+      <c r="C8" s="7" t="inlineStr">
+        <is>
+          <t>不是</t>
+        </is>
+      </c>
+      <c r="D8" s="7" t="inlineStr">
         <is>
           <t>慣性</t>
         </is>
       </c>
-      <c r="D8" s="7" t="inlineStr">
+      <c r="E8" s="7" t="inlineStr">
+        <is>
+          <t>保持靜止</t>
+        </is>
+      </c>
+      <c r="F8" s="7" t="inlineStr">
+        <is>
+          <t>零</t>
+        </is>
+      </c>
+      <c r="G8" s="8" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H8" s="7" t="inlineStr">
         <is>
           <t>甩動</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="34" customHeight="1">
+    <row r="9" ht="40" customHeight="1">
       <c r="A9" s="3" t="n">
         <v>7</v>
       </c>
@@ -909,18 +1277,38 @@
           <t>靜止物體有慣性嗎？</t>
         </is>
       </c>
-      <c r="C9" s="5" t="inlineStr">
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>慣性維持靜止</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="inlineStr">
+        <is>
+          <t>等速直線運動</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr">
+        <is>
+          <t>零</t>
+        </is>
+      </c>
+      <c r="F9" s="4" t="inlineStr">
         <is>
           <t>有</t>
         </is>
       </c>
-      <c r="D9" s="4" t="inlineStr">
+      <c r="G9" s="5" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H9" s="4" t="inlineStr">
         <is>
           <t>維持靜止</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="34" customHeight="1">
+    <row r="10" ht="40" customHeight="1">
       <c r="A10" s="6" t="n">
         <v>8</v>
       </c>
@@ -929,18 +1317,38 @@
           <t>合力為零物體加速度？</t>
         </is>
       </c>
-      <c r="C10" s="8" t="inlineStr">
+      <c r="C10" s="7" t="inlineStr">
         <is>
           <t>零</t>
         </is>
       </c>
       <c r="D10" s="7" t="inlineStr">
         <is>
+          <t>不是</t>
+        </is>
+      </c>
+      <c r="E10" s="7" t="inlineStr">
+        <is>
+          <t>慣性維持前進</t>
+        </is>
+      </c>
+      <c r="F10" s="7" t="inlineStr">
+        <is>
+          <t>保持靜止</t>
+        </is>
+      </c>
+      <c r="G10" s="8" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H10" s="7" t="inlineStr">
+        <is>
           <t>等速或靜止</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="34" customHeight="1">
+    <row r="11" ht="40" customHeight="1">
       <c r="A11" s="3" t="n">
         <v>9</v>
       </c>
@@ -949,18 +1357,38 @@
           <t>突然剎車人向前衝是因為？</t>
         </is>
       </c>
-      <c r="C11" s="5" t="inlineStr">
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>越大</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="inlineStr">
         <is>
           <t>慣性</t>
         </is>
       </c>
-      <c r="D11" s="4" t="inlineStr">
+      <c r="E11" s="4" t="inlineStr">
+        <is>
+          <t>質量</t>
+        </is>
+      </c>
+      <c r="F11" s="4" t="inlineStr">
+        <is>
+          <t>第一</t>
+        </is>
+      </c>
+      <c r="G11" s="5" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H11" s="4" t="inlineStr">
         <is>
           <t>慣性</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="34" customHeight="1">
+    <row r="12" ht="40" customHeight="1">
       <c r="A12" s="6" t="n">
         <v>10</v>
       </c>
@@ -969,12 +1397,32 @@
           <t>質量大的物體慣性？</t>
         </is>
       </c>
-      <c r="C12" s="8" t="inlineStr">
+      <c r="C12" s="7" t="inlineStr">
+        <is>
+          <t>有</t>
+        </is>
+      </c>
+      <c r="D12" s="7" t="inlineStr">
+        <is>
+          <t>保持靜止</t>
+        </is>
+      </c>
+      <c r="E12" s="7" t="inlineStr">
         <is>
           <t>大</t>
         </is>
       </c>
-      <c r="D12" s="7" t="inlineStr">
+      <c r="F12" s="7" t="inlineStr">
+        <is>
+          <t>等速直線運動</t>
+        </is>
+      </c>
+      <c r="G12" s="8" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H12" s="7" t="inlineStr">
         <is>
           <t>量度</t>
         </is>
@@ -982,7 +1430,7 @@
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A1:H1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -994,19 +1442,23 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D12"/>
+  <dimension ref="A1:H12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
-    <col width="62" customWidth="1" min="2" max="2"/>
+    <col width="54" customWidth="1" min="2" max="2"/>
     <col width="20" customWidth="1" min="3" max="3"/>
-    <col width="42" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="8" customWidth="1" min="7" max="7"/>
+    <col width="40" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>國三上學期 九上2-1 牛頓第一運動定律　測驗　★★★ 挑戰（評鑑・創造）</t>
+          <t>國三上學期 九上2-1 牛頓第一運動定律　測驗　★★★ 挑戰（評鑑・創造）（四選一單選）</t>
         </is>
       </c>
     </row>
@@ -1023,16 +1475,36 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
+          <t>(A)</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>(B)</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>(C)</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>(D)</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
           <t>答案</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="H2" s="2" t="inlineStr">
         <is>
           <t>解析</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="34" customHeight="1">
+    <row r="3" ht="40" customHeight="1">
       <c r="A3" s="3" t="n">
         <v>1</v>
       </c>
@@ -1041,18 +1513,38 @@
           <t>為何說質量是慣性的量度？</t>
         </is>
       </c>
-      <c r="C3" s="5" t="inlineStr">
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>維持等速直線(或靜止)</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>慣性使車無法立即停下</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
         <is>
           <t>質量越大越難改變運動狀態</t>
         </is>
       </c>
-      <c r="D3" s="4" t="inlineStr">
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>不受外力或合力為零</t>
+        </is>
+      </c>
+      <c r="G3" s="5" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H3" s="4" t="inlineStr">
         <is>
           <t>量度</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="34" customHeight="1">
+    <row r="4" ht="40" customHeight="1">
       <c r="A4" s="6" t="n">
         <v>2</v>
       </c>
@@ -1061,18 +1553,38 @@
           <t>用慣性解釋安全帶與頭枕的作用？</t>
         </is>
       </c>
-      <c r="C4" s="8" t="inlineStr">
+      <c r="C4" s="7" t="inlineStr">
+        <is>
+          <t>身體慣性維持原方向</t>
+        </is>
+      </c>
+      <c r="D4" s="7" t="inlineStr">
+        <is>
+          <t>維持等速直線(或靜止)</t>
+        </is>
+      </c>
+      <c r="E4" s="7" t="inlineStr">
         <is>
           <t>防止碰撞時身體因慣性前衝或後仰受傷</t>
         </is>
       </c>
-      <c r="D4" s="7" t="inlineStr">
+      <c r="F4" s="7" t="inlineStr">
+        <is>
+          <t>不受外力或合力為零</t>
+        </is>
+      </c>
+      <c r="G4" s="8" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H4" s="7" t="inlineStr">
         <is>
           <t>應用</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="34" customHeight="1">
+    <row r="5" ht="40" customHeight="1">
       <c r="A5" s="3" t="n">
         <v>3</v>
       </c>
@@ -1081,18 +1593,38 @@
           <t>太空中物體不受力會如何運動？</t>
         </is>
       </c>
-      <c r="C5" s="5" t="inlineStr">
+      <c r="C5" s="4" t="inlineStr">
         <is>
           <t>維持等速直線(或靜止)</t>
         </is>
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
+          <t>身體慣性維持原方向</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>防止碰撞時身體因慣性前衝或後仰受傷</t>
+        </is>
+      </c>
+      <c r="F5" s="4" t="inlineStr">
+        <is>
+          <t>質量越大越難改變運動狀態</t>
+        </is>
+      </c>
+      <c r="G5" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H5" s="4" t="inlineStr">
+        <is>
           <t>慣性</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="34" customHeight="1">
+    <row r="6" ht="40" customHeight="1">
       <c r="A6" s="6" t="n">
         <v>4</v>
       </c>
@@ -1101,18 +1633,38 @@
           <t>急轉彎乘客往外傾用慣性解釋？</t>
         </is>
       </c>
-      <c r="C6" s="8" t="inlineStr">
+      <c r="C6" s="7" t="inlineStr">
+        <is>
+          <t>不受外力或合力為零</t>
+        </is>
+      </c>
+      <c r="D6" s="7" t="inlineStr">
+        <is>
+          <t>質量越大越難改變運動狀態</t>
+        </is>
+      </c>
+      <c r="E6" s="7" t="inlineStr">
         <is>
           <t>身體慣性維持原方向</t>
         </is>
       </c>
-      <c r="D6" s="7" t="inlineStr">
+      <c r="F6" s="7" t="inlineStr">
+        <is>
+          <t>卡車,質量大慣性大</t>
+        </is>
+      </c>
+      <c r="G6" s="8" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H6" s="7" t="inlineStr">
         <is>
           <t>慣性</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="34" customHeight="1">
+    <row r="7" ht="40" customHeight="1">
       <c r="A7" s="3" t="n">
         <v>5</v>
       </c>
@@ -1121,18 +1673,38 @@
           <t>慣性定律成立條件是？</t>
         </is>
       </c>
-      <c r="C7" s="5" t="inlineStr">
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>防止碰撞時身體因慣性前衝或後仰受傷</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>身體慣性維持原方向</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>質量越大越難改變運動狀態</t>
+        </is>
+      </c>
+      <c r="F7" s="4" t="inlineStr">
         <is>
           <t>不受外力或合力為零</t>
         </is>
       </c>
-      <c r="D7" s="4" t="inlineStr">
+      <c r="G7" s="5" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H7" s="4" t="inlineStr">
         <is>
           <t>條件</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="34" customHeight="1">
+    <row r="8" ht="40" customHeight="1">
       <c r="A8" s="6" t="n">
         <v>6</v>
       </c>
@@ -1141,18 +1713,38 @@
           <t>拍打衣服除塵原理？</t>
         </is>
       </c>
-      <c r="C8" s="8" t="inlineStr">
+      <c r="C8" s="7" t="inlineStr">
+        <is>
+          <t>維持等速直線(或靜止)</t>
+        </is>
+      </c>
+      <c r="D8" s="7" t="inlineStr">
+        <is>
+          <t>質量越大越難改變運動狀態</t>
+        </is>
+      </c>
+      <c r="E8" s="7" t="inlineStr">
         <is>
           <t>衣停灰塵因慣性續動而分離</t>
         </is>
       </c>
-      <c r="D8" s="7" t="inlineStr">
+      <c r="F8" s="7" t="inlineStr">
+        <is>
+          <t>身體慣性維持原方向</t>
+        </is>
+      </c>
+      <c r="G8" s="8" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H8" s="7" t="inlineStr">
         <is>
           <t>慣性</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="34" customHeight="1">
+    <row r="9" ht="40" customHeight="1">
       <c r="A9" s="3" t="n">
         <v>7</v>
       </c>
@@ -1161,18 +1753,38 @@
           <t>為何等速運動不需持續施力？</t>
         </is>
       </c>
-      <c r="C9" s="5" t="inlineStr">
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>防止碰撞時身體因慣性前衝或後仰受傷</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="inlineStr">
         <is>
           <t>慣性使其維持,無需力</t>
         </is>
       </c>
-      <c r="D9" s="4" t="inlineStr">
+      <c r="E9" s="4" t="inlineStr">
+        <is>
+          <t>身體慣性維持原方向</t>
+        </is>
+      </c>
+      <c r="F9" s="4" t="inlineStr">
+        <is>
+          <t>維持等速直線(或靜止)</t>
+        </is>
+      </c>
+      <c r="G9" s="5" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H9" s="4" t="inlineStr">
         <is>
           <t>觀念</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="34" customHeight="1">
+    <row r="10" ht="40" customHeight="1">
       <c r="A10" s="6" t="n">
         <v>8</v>
       </c>
@@ -1181,18 +1793,38 @@
           <t>比較同速的卡車與腳踏車何者難停?為何</t>
         </is>
       </c>
-      <c r="C10" s="8" t="inlineStr">
+      <c r="C10" s="7" t="inlineStr">
+        <is>
+          <t>防止碰撞時身體因慣性前衝或後仰受傷</t>
+        </is>
+      </c>
+      <c r="D10" s="7" t="inlineStr">
+        <is>
+          <t>質量越大越難改變運動狀態</t>
+        </is>
+      </c>
+      <c r="E10" s="7" t="inlineStr">
+        <is>
+          <t>身體慣性維持原方向</t>
+        </is>
+      </c>
+      <c r="F10" s="7" t="inlineStr">
         <is>
           <t>卡車,質量大慣性大</t>
         </is>
       </c>
-      <c r="D10" s="7" t="inlineStr">
+      <c r="G10" s="8" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H10" s="7" t="inlineStr">
         <is>
           <t>質量</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="34" customHeight="1">
+    <row r="11" ht="40" customHeight="1">
       <c r="A11" s="3" t="n">
         <v>9</v>
       </c>
@@ -1201,18 +1833,38 @@
           <t>太空中輕推衛星後它會？</t>
         </is>
       </c>
-      <c r="C11" s="5" t="inlineStr">
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>等速直線運動</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="inlineStr">
         <is>
           <t>持續等速前進</t>
         </is>
       </c>
-      <c r="D11" s="4" t="inlineStr">
+      <c r="E11" s="4" t="inlineStr">
+        <is>
+          <t>質量大慣性大</t>
+        </is>
+      </c>
+      <c r="F11" s="4" t="inlineStr">
+        <is>
+          <t>第一</t>
+        </is>
+      </c>
+      <c r="G11" s="5" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H11" s="4" t="inlineStr">
         <is>
           <t>慣性</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="34" customHeight="1">
+    <row r="12" ht="40" customHeight="1">
       <c r="A12" s="6" t="n">
         <v>10</v>
       </c>
@@ -1221,12 +1873,32 @@
           <t>行車保持安全距離與慣性的關係？</t>
         </is>
       </c>
-      <c r="C12" s="8" t="inlineStr">
+      <c r="C12" s="7" t="inlineStr">
         <is>
           <t>慣性使車無法立即停下</t>
         </is>
       </c>
       <c r="D12" s="7" t="inlineStr">
+        <is>
+          <t>身體慣性維持原方向</t>
+        </is>
+      </c>
+      <c r="E12" s="7" t="inlineStr">
+        <is>
+          <t>質量越大越難改變運動狀態</t>
+        </is>
+      </c>
+      <c r="F12" s="7" t="inlineStr">
+        <is>
+          <t>慣性使其維持,無需力</t>
+        </is>
+      </c>
+      <c r="G12" s="8" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H12" s="7" t="inlineStr">
         <is>
           <t>慣性</t>
         </is>
@@ -1234,7 +1906,7 @@
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A1:H1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/02_加值成品/九上/九上2-1_三種難度測驗卷.xlsx
+++ b/02_加值成品/九上/九上2-1_三種難度測驗卷.xlsx
@@ -588,7 +588,7 @@
       </c>
       <c r="H3" s="4" t="inlineStr">
         <is>
-          <t>固有</t>
+          <t>固有：每個物體天生就有想保持原本運動狀態的性質,叫做慣性</t>
         </is>
       </c>
     </row>
@@ -628,7 +628,7 @@
       </c>
       <c r="H4" s="7" t="inlineStr">
         <is>
-          <t>靜者恆靜</t>
+          <t>靜者恆靜：沒有外力推它,靜止的物體會一直維持不動</t>
         </is>
       </c>
     </row>
@@ -668,7 +668,7 @@
       </c>
       <c r="H5" s="4" t="inlineStr">
         <is>
-          <t>動者恆動</t>
+          <t>動者恆動：沒有外力改變它,運動中的物體會一直維持等速前進</t>
         </is>
       </c>
     </row>
@@ -708,7 +708,7 @@
       </c>
       <c r="H6" s="7" t="inlineStr">
         <is>
-          <t>慣性</t>
+          <t>慣性：牛頓提出的第一運動定律就是在說明慣性這件事</t>
         </is>
       </c>
     </row>
@@ -748,7 +748,7 @@
       </c>
       <c r="H7" s="4" t="inlineStr">
         <is>
-          <t>量度</t>
+          <t>量度：物體的質量越大,慣性就越大,質量就是慣性的量度</t>
         </is>
       </c>
     </row>
@@ -788,7 +788,7 @@
       </c>
       <c r="H8" s="7" t="inlineStr">
         <is>
-          <t>越難改變</t>
+          <t>越難改變：質量越大的物體越不容易被改變運動狀態</t>
         </is>
       </c>
     </row>
@@ -828,7 +828,7 @@
       </c>
       <c r="H9" s="4" t="inlineStr">
         <is>
-          <t>慣性</t>
+          <t>慣性：靠慣性就能一直保持等速前進,不需要外力持續推</t>
         </is>
       </c>
     </row>
@@ -868,7 +868,7 @@
       </c>
       <c r="H10" s="7" t="inlineStr">
         <is>
-          <t>保護</t>
+          <t>保護：車子突然停下時,人因為慣性會繼續往前衝,安全帶能擋住這個衝力</t>
         </is>
       </c>
     </row>
@@ -908,7 +908,7 @@
       </c>
       <c r="H11" s="4" t="inlineStr">
         <is>
-          <t>慣性</t>
+          <t>慣性：牛頓第一運動定律又叫慣性定律,說明物體有維持原本運動狀態的傾向</t>
         </is>
       </c>
     </row>
@@ -948,7 +948,7 @@
       </c>
       <c r="H12" s="7" t="inlineStr">
         <is>
-          <t>慣性</t>
+          <t>慣性：根據慣性定律,沒有外力作用時,靜止的物體會繼續靜止,運動的物體會繼續等速前進</t>
         </is>
       </c>
     </row>
@@ -1064,7 +1064,7 @@
       </c>
       <c r="H3" s="4" t="inlineStr">
         <is>
-          <t>慣性</t>
+          <t>慣性：車子停下來了,但乘客身體因為慣性還想繼續往前,所以會前傾</t>
         </is>
       </c>
     </row>
@@ -1104,7 +1104,7 @@
       </c>
       <c r="H4" s="7" t="inlineStr">
         <is>
-          <t>慣性</t>
+          <t>慣性：公車突然往前開,但乘客身體因為慣性還想保持靜止,所以往後倒</t>
         </is>
       </c>
     </row>
@@ -1144,7 +1144,7 @@
       </c>
       <c r="H5" s="4" t="inlineStr">
         <is>
-          <t>性質</t>
+          <t>性質：慣性不是一種推或拉的力,而是物體本身固有的一種特性</t>
         </is>
       </c>
     </row>
@@ -1184,7 +1184,7 @@
       </c>
       <c r="H6" s="7" t="inlineStr">
         <is>
-          <t>質量</t>
+          <t>質量：大貨車質量比機車大很多,慣性也大很多,所以更難讓它停下來</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="H7" s="4" t="inlineStr">
         <is>
-          <t>無阻力</t>
+          <t>無阻力：太空中沒有摩擦力和空氣阻力,推一下後物體會靠慣性一直等速前進</t>
         </is>
       </c>
     </row>
@@ -1264,7 +1264,7 @@
       </c>
       <c r="H8" s="7" t="inlineStr">
         <is>
-          <t>甩動</t>
+          <t>甩動：手臂突然停止甩動時,水銀因為慣性繼續往下移動</t>
         </is>
       </c>
     </row>
@@ -1304,7 +1304,7 @@
       </c>
       <c r="H9" s="4" t="inlineStr">
         <is>
-          <t>維持靜止</t>
+          <t>維持靜止：靜止也是一種運動狀態,靜止的物體同樣有想保持不動的慣性</t>
         </is>
       </c>
     </row>
@@ -1344,7 +1344,7 @@
       </c>
       <c r="H10" s="7" t="inlineStr">
         <is>
-          <t>等速或靜止</t>
+          <t>等速或靜止：沒有淨力作用,速度就不會改變,加速度自然是零</t>
         </is>
       </c>
     </row>
@@ -1384,7 +1384,7 @@
       </c>
       <c r="H11" s="4" t="inlineStr">
         <is>
-          <t>慣性</t>
+          <t>慣性：車子突然減速時,人的身體因為慣性想維持原本前進的速度,所以會向前傾倒</t>
         </is>
       </c>
     </row>
@@ -1424,7 +1424,7 @@
       </c>
       <c r="H12" s="7" t="inlineStr">
         <is>
-          <t>量度</t>
+          <t>量度：質量是慣性大小的量度,質量越大的物體越難改變運動狀態,慣性也越大</t>
         </is>
       </c>
     </row>
@@ -1540,7 +1540,7 @@
       </c>
       <c r="H3" s="4" t="inlineStr">
         <is>
-          <t>量度</t>
+          <t>量度：要讓質量大的物體改變運動狀態需要更大的力,所以質量能代表慣性大小</t>
         </is>
       </c>
     </row>
@@ -1580,7 +1580,7 @@
       </c>
       <c r="H4" s="7" t="inlineStr">
         <is>
-          <t>應用</t>
+          <t>應用：撞擊瞬間身體因慣性想繼續原本的運動,安全帶頭枕能限制身體亂動而受傷</t>
         </is>
       </c>
     </row>
@@ -1620,7 +1620,7 @@
       </c>
       <c r="H5" s="4" t="inlineStr">
         <is>
-          <t>慣性</t>
+          <t>慣性：完全沒有外力作用時,物體會照著慣性,原本靜止就繼續靜止,原本動就一直等速前進</t>
         </is>
       </c>
     </row>
@@ -1660,7 +1660,7 @@
       </c>
       <c r="H6" s="7" t="inlineStr">
         <is>
-          <t>慣性</t>
+          <t>慣性：車子轉彎了,但乘客身體因慣性還想繼續走原本的直線方向,所以感覺被甩向外側</t>
         </is>
       </c>
     </row>
@@ -1700,7 +1700,7 @@
       </c>
       <c r="H7" s="4" t="inlineStr">
         <is>
-          <t>條件</t>
+          <t>條件：只有在物體完全不受力,或者所有受力互相抵消合力為零時,慣性定律才成立</t>
         </is>
       </c>
     </row>
@@ -1740,7 +1740,7 @@
       </c>
       <c r="H8" s="7" t="inlineStr">
         <is>
-          <t>慣性</t>
+          <t>慣性：拍打讓衣服瞬間停下,但灰塵因慣性還想繼續運動,兩者因此分開脫落</t>
         </is>
       </c>
     </row>
@@ -1780,7 +1780,7 @@
       </c>
       <c r="H9" s="4" t="inlineStr">
         <is>
-          <t>觀念</t>
+          <t>觀念：只要沒有阻力來改變它,物體靠慣性本身就能一直保持等速前進的狀態</t>
         </is>
       </c>
     </row>
@@ -1820,7 +1820,7 @@
       </c>
       <c r="H10" s="7" t="inlineStr">
         <is>
-          <t>質量</t>
+          <t>質量：速度相同時,卡車質量遠大於腳踏車,慣性也大很多,所以更難讓它停下來</t>
         </is>
       </c>
     </row>
@@ -1860,7 +1860,7 @@
       </c>
       <c r="H11" s="4" t="inlineStr">
         <is>
-          <t>慣性</t>
+          <t>慣性：太空中幾乎沒有摩擦力和空氣阻力,衛星一旦被推動,會依慣性定律持續以等速度前進</t>
         </is>
       </c>
     </row>
@@ -1900,7 +1900,7 @@
       </c>
       <c r="H12" s="7" t="inlineStr">
         <is>
-          <t>慣性</t>
+          <t>慣性：行進中的車輛因為慣性,踩煞車後不會馬上停止,需要保持安全距離以免追撞</t>
         </is>
       </c>
     </row>

--- a/02_加值成品/九上/九上2-1_三種難度測驗卷.xlsx
+++ b/02_加值成品/九上/九上2-1_三種難度測驗卷.xlsx
@@ -563,7 +563,7 @@
       </c>
       <c r="C3" s="4" t="inlineStr">
         <is>
-          <t>等速前進</t>
+          <t>等速直線運動</t>
         </is>
       </c>
       <c r="D3" s="4" t="inlineStr">
@@ -573,12 +573,12 @@
       </c>
       <c r="E3" s="4" t="inlineStr">
         <is>
-          <t>第一</t>
+          <t>保持靜止</t>
         </is>
       </c>
       <c r="F3" s="4" t="inlineStr">
         <is>
-          <t>前衝</t>
+          <t>有</t>
         </is>
       </c>
       <c r="G3" s="5" t="inlineStr">
@@ -728,17 +728,17 @@
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>不是</t>
+          <t>大</t>
         </is>
       </c>
       <c r="E7" s="4" t="inlineStr">
         <is>
+          <t>慣性維持前進</t>
+        </is>
+      </c>
+      <c r="F7" s="4" t="inlineStr">
+        <is>
           <t>等速直線運動</t>
-        </is>
-      </c>
-      <c r="F7" s="4" t="inlineStr">
-        <is>
-          <t>保持靜止</t>
         </is>
       </c>
       <c r="G7" s="5" t="inlineStr">
@@ -763,12 +763,12 @@
       </c>
       <c r="C8" s="7" t="inlineStr">
         <is>
-          <t>持續等速前進</t>
+          <t>保持靜止</t>
         </is>
       </c>
       <c r="D8" s="7" t="inlineStr">
         <is>
-          <t>質量大慣性大</t>
+          <t>等速直線運動</t>
         </is>
       </c>
       <c r="E8" s="7" t="inlineStr">
@@ -778,7 +778,7 @@
       </c>
       <c r="F8" s="7" t="inlineStr">
         <is>
-          <t>等速直線運動</t>
+          <t>不是</t>
         </is>
       </c>
       <c r="G8" s="8" t="inlineStr">
@@ -1039,12 +1039,12 @@
       </c>
       <c r="C3" s="4" t="inlineStr">
         <is>
-          <t>等速前進</t>
+          <t>質量大慣性大</t>
         </is>
       </c>
       <c r="D3" s="4" t="inlineStr">
         <is>
-          <t>慣性</t>
+          <t>第一</t>
         </is>
       </c>
       <c r="E3" s="4" t="inlineStr">
@@ -1054,7 +1054,7 @@
       </c>
       <c r="F3" s="4" t="inlineStr">
         <is>
-          <t>第一</t>
+          <t>質量</t>
         </is>
       </c>
       <c r="G3" s="5" t="inlineStr">
@@ -1084,17 +1084,17 @@
       </c>
       <c r="D4" s="7" t="inlineStr">
         <is>
-          <t>慣性</t>
+          <t>第一</t>
         </is>
       </c>
       <c r="E4" s="7" t="inlineStr">
         <is>
+          <t>保持靜止</t>
+        </is>
+      </c>
+      <c r="F4" s="7" t="inlineStr">
+        <is>
           <t>質量</t>
-        </is>
-      </c>
-      <c r="F4" s="7" t="inlineStr">
-        <is>
-          <t>第一</t>
         </is>
       </c>
       <c r="G4" s="8" t="inlineStr">
@@ -1164,7 +1164,7 @@
       </c>
       <c r="D6" s="7" t="inlineStr">
         <is>
-          <t>不需要</t>
+          <t>持續等速前進</t>
         </is>
       </c>
       <c r="E6" s="7" t="inlineStr">
@@ -1174,7 +1174,7 @@
       </c>
       <c r="F6" s="7" t="inlineStr">
         <is>
-          <t>維持不變</t>
+          <t>零</t>
         </is>
       </c>
       <c r="G6" s="8" t="inlineStr">
@@ -1199,17 +1199,17 @@
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t>等速直線運動</t>
+          <t>保持靜止</t>
         </is>
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>慣性</t>
+          <t>質量</t>
         </is>
       </c>
       <c r="E7" s="4" t="inlineStr">
         <is>
-          <t>維持不變</t>
+          <t>前衝</t>
         </is>
       </c>
       <c r="F7" s="4" t="inlineStr">
@@ -1239,7 +1239,7 @@
       </c>
       <c r="C8" s="7" t="inlineStr">
         <is>
-          <t>不是</t>
+          <t>等速直線運動</t>
         </is>
       </c>
       <c r="D8" s="7" t="inlineStr">
@@ -1249,12 +1249,12 @@
       </c>
       <c r="E8" s="7" t="inlineStr">
         <is>
-          <t>保持靜止</t>
+          <t>零</t>
         </is>
       </c>
       <c r="F8" s="7" t="inlineStr">
         <is>
-          <t>零</t>
+          <t>質量</t>
         </is>
       </c>
       <c r="G8" s="8" t="inlineStr">
@@ -1359,7 +1359,7 @@
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>越大</t>
+          <t>等速前進</t>
         </is>
       </c>
       <c r="D11" s="4" t="inlineStr">
@@ -1369,12 +1369,12 @@
       </c>
       <c r="E11" s="4" t="inlineStr">
         <is>
-          <t>質量</t>
+          <t>大</t>
         </is>
       </c>
       <c r="F11" s="4" t="inlineStr">
         <is>
-          <t>第一</t>
+          <t>前衝</t>
         </is>
       </c>
       <c r="G11" s="5" t="inlineStr">
@@ -1399,7 +1399,7 @@
       </c>
       <c r="C12" s="7" t="inlineStr">
         <is>
-          <t>有</t>
+          <t>慣性維持靜止</t>
         </is>
       </c>
       <c r="D12" s="7" t="inlineStr">
@@ -1414,7 +1414,7 @@
       </c>
       <c r="F12" s="7" t="inlineStr">
         <is>
-          <t>等速直線運動</t>
+          <t>第一</t>
         </is>
       </c>
       <c r="G12" s="8" t="inlineStr">
@@ -1835,7 +1835,7 @@
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>等速直線運動</t>
+          <t>保持靜止</t>
         </is>
       </c>
       <c r="D11" s="4" t="inlineStr">
@@ -1845,12 +1845,12 @@
       </c>
       <c r="E11" s="4" t="inlineStr">
         <is>
-          <t>質量大慣性大</t>
+          <t>越大</t>
         </is>
       </c>
       <c r="F11" s="4" t="inlineStr">
         <is>
-          <t>第一</t>
+          <t>零</t>
         </is>
       </c>
       <c r="G11" s="5" t="inlineStr">
